--- a/data/trans_dic/P64D1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D1_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 50,18</t>
+          <t>30,3; 59,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 46,99</t>
+          <t>21,87; 46,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,27; 43,21</t>
+          <t>28,52; 49,85</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,71; 27,71</t>
+          <t>16,48; 27,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,75; 74,46</t>
+          <t>32,14; 43,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,28; 54,52</t>
+          <t>24,34; 32,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 25,6</t>
+          <t>19,2; 27,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31,04; 39,0</t>
+          <t>32,25; 40,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 30,3</t>
+          <t>25,85; 31,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 23,02</t>
+          <t>19,31; 26,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,2; 38,19</t>
+          <t>31,75; 38,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 28,42</t>
+          <t>25,97; 31,27</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,24; 32,61</t>
+          <t>22,24; 31,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,54; 50,97</t>
+          <t>40,9; 51,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,56; 38,72</t>
+          <t>31,01; 38,37</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,64%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,62; 75,14</t>
+          <t>35,75; 74,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,5; 75,86</t>
+          <t>40,1; 72,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45,67; 70,29</t>
+          <t>41,24; 67,76</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 24,34</t>
+          <t>22,56; 26,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,38; 48,59</t>
+          <t>35,56; 39,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,33</t>
+          <t>28,84; 31,94</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>46003</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56029</t>
+          <t>76604</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17053; 45470</t>
+          <t>31763; 62324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16979; 38177</t>
+          <t>20065; 42780</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39996; 74262</t>
+          <t>56058; 97996</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>84624</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>169975</t>
+          <t>118871</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243945</t>
+          <t>203496</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58556; 97083</t>
+          <t>65255; 108020</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118016; 260386</t>
+          <t>101269; 135810</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184007; 381669</t>
+          <t>173084; 229620</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>100673</t>
+          <t>123032</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>122608</t>
+          <t>143447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>223282</t>
+          <t>266479</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84375; 118271</t>
+          <t>102983; 144973</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>109000; 136965</t>
+          <t>128029; 159717</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201943; 246386</t>
+          <t>241276; 293104</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>110931</t>
+          <t>124578</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>150686</t>
+          <t>159841</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261617</t>
+          <t>284419</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41597; 171545</t>
+          <t>104984; 144642</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118633; 172962</t>
+          <t>144447; 176880</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>127216; 340470</t>
+          <t>259353; 312271</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>82255</t>
+          <t>87515</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96039</t>
+          <t>106566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178293</t>
+          <t>194082</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>69510; 97538</t>
+          <t>72800; 103390</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>84385; 106090</t>
+          <t>95180; 118974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160087; 196402</t>
+          <t>173712; 214905</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>21636</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6204; 12731</t>
+          <t>6852; 14282</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7899; 13466</t>
+          <t>7908; 14229</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15846; 24385</t>
+          <t>16037; 26349</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>274125; 478461</t>
+          <t>435206; 519577</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>516941; 709865</t>
+          <t>537411; 603879</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>808557; 1142099</t>
+          <t>992323; 1098725</t>
         </is>
       </c>
     </row>
